--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/NEW_JERSEY_2018.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/NEW_JERSEY_2018.xlsx
@@ -4092,7 +4092,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C208">
@@ -8635,7 +8635,7 @@
         <v>130</v>
       </c>
       <c r="D460">
-        <v>0.009369369369369369</v>
+        <v>0.009369369369369367</v>
       </c>
     </row>
     <row r="461">
@@ -11256,7 +11256,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C606">
@@ -12228,7 +12228,7 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C660">
@@ -12354,7 +12354,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C667">
@@ -20202,7 +20202,7 @@
       </c>
       <c r="B1103" t="inlineStr">
         <is>
-          <t>Ziltlaltepec De Trinidad Sanchez Santos</t>
+          <t>Zitlaltepec De Trinidad Sanchez Santos</t>
         </is>
       </c>
       <c r="C1103">
